--- a/sheets/대금율보/검수/청성해탄곡 (b2_159_1).xlsx
+++ b/sheets/대금율보/검수/청성해탄곡 (b2_159_1).xlsx
@@ -5267,11 +5267,7 @@
         </is>
       </c>
       <c r="C10" s="22"/>
-      <c r="D10" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+      <c r="D10" s="25"/>
       <c r="E10" s="26"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
@@ -5587,11 +5583,7 @@
         </is>
       </c>
       <c r="E15" s="22"/>
-      <c r="F15" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">?</t>
-        </is>
-      </c>
+      <c r="F15" s="25"/>
       <c r="G15" s="26"/>
       <c r="H15" s="21" t="inlineStr">
         <is>

--- a/sheets/대금율보/검수/청성해탄곡 (b2_159_1).xlsx
+++ b/sheets/대금율보/검수/청성해탄곡 (b2_159_1).xlsx
@@ -4764,30 +4764,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="15.29" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="15.29" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="15.29" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="15.29" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="15.29" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="15.29" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="15.29" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="15.29" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="15.29" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="95.24" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="106.52" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="106.52" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
       <c r="R4" s="21"/>
       <c r="S4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="106.52" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="S5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="106.52" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="106.52" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="106.52" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="S8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="106.52" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="106.52" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
       </c>
       <c r="S10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="106.52" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="106.52" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="106.52" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="S13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="106.52" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
       </c>
       <c r="S14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="106.52" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -5626,7 +5626,7 @@
       <c r="R15" s="21"/>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="106.52" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="22"/>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="S16" s="22"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="106.52" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="22"/>
@@ -5740,7 +5740,7 @@
       </c>
       <c r="S17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="106.52" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="22"/>
@@ -5809,6 +5809,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="67"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="42"/>
 </worksheet>
 </file>